--- a/scripts/recalc/subset.xlsx
+++ b/scripts/recalc/subset.xlsx
@@ -11,7 +11,7 @@
     <sheet name="math" sheetId="4" r:id="rIdFrazaro4"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.8.0; sentences sha256:AC5301DBC1F55220FFDA023604667E1AB429335BDA03D9902519B1335DA93B37 over 4455 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.8.1; sentences sha256:AC5301DBC1F55220FFDA023604667E1AB429335BDA03D9902519B1335DA93B37 over 4455 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -1675,6 +1675,7 @@
       </c>
       <c r="C1" s="0">
         <f>A1+A2</f>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
@@ -1685,19 +1686,23 @@
       </c>
       <c r="C2" s="0">
         <f>A1+A3</f>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0">
+      <c r="A3" s="0" t="b">
         <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="C3" s="0">
         <f>A1+A4</f>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="0">
+      <c r="C4" s="0" t="e">
         <f>A1+A5</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5">
@@ -1706,147 +1711,174 @@
           <t xml:space="preserve">abc</t>
         </is>
       </c>
-      <c r="C5" s="0">
+      <c r="C5" s="0" t="str">
         <f>A1&amp;A2</f>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
         <v>0.1</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6" s="0" t="str">
         <f>A6+A7&amp;""</f>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
         <v>0.2</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C7" s="0" t="str">
         <f>A3&amp;""</f>
+        <v>TRUE</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
         <v>-2</v>
       </c>
-      <c r="C8" s="0">
+      <c r="C8" s="0" t="b">
         <f>A1=A2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="0">
+      <c r="C9" s="0" t="b">
         <f>A1&lt;A5</f>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="0">
+      <c r="C10" s="0" t="b">
         <f>A3&gt;A5</f>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="0">
+      <c r="C11" s="0" t="b">
         <f>"ABC"="abc"</f>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="0">
+      <c r="C12" s="0" t="b">
         <f>A4=0</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="0">
+      <c r="C13" s="0" t="b">
         <f>A4=""</f>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="0">
         <f>-A8^2</f>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="C15" s="0">
         <f>2^3^2</f>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="0">
+      <c r="C16" s="0" t="e">
         <f>A1/A4</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="0">
+      <c r="C17" s="0" t="e">
         <f>0^0</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="18">
       <c r="C18" s="0">
         <f>50%</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
       <c r="C19" s="0">
         <f>A2*2</f>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="0">
+      <c r="C20" s="0" t="str">
         <f>1/3&amp;""</f>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="0">
+      <c r="C21" s="0" t="str">
         <f>0.0000001&amp;""</f>
+        <v>0.0000001</v>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="0">
+      <c r="C22" s="0" t="str">
         <f>10^21&amp;""</f>
+        <v>1E+21</v>
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="0">
+      <c r="C23" s="0" t="str">
         <f>10^20&amp;""</f>
+        <v>1E+20</v>
       </c>
     </row>
     <row r="24">
       <c r="C24" s="0">
         <f>-"5"</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="0">
+      <c r="C25" s="0" t="str">
         <f>+"5"</f>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="0">
+      <c r="C26" s="0" t="e">
         <f>1E307*100</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="0">
         <f>(1=1)+1</f>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="0">
+      <c r="C28" s="0" t="e">
         <f>A8^0.5</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="29">
-      <c r="C29" s="0">
+      <c r="C29" s="0" t="e">
         <f>0^-1</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="30">
-      <c r="C30" s="0">
+      <c r="C30" s="0" t="b">
         <f>A2=7</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="0">
+      <c r="C31" s="0" t="b">
         <f>A1&lt;&gt;A4</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1862,8 +1894,9 @@
       <c r="A1" s="0">
         <v>10</v>
       </c>
-      <c r="C1" s="0">
+      <c r="C1" s="0" t="str">
         <f>IF(A1&gt;5,"big","small")</f>
+        <v>big</v>
       </c>
     </row>
     <row r="2">
@@ -1872,6 +1905,7 @@
       </c>
       <c r="C2" s="0">
         <f>IF(A5,1,2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1880,16 +1914,19 @@
           <t xml:space="preserve">x</t>
         </is>
       </c>
-      <c r="C3" s="0">
+      <c r="C3" s="0" t="e">
         <f>IF(A3,1,2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0">
+      <c r="A4" s="0" t="b">
         <f>TRUE</f>
-      </c>
-      <c r="C4" s="0">
+        <v>1</v>
+      </c>
+      <c r="C4" s="0" t="b">
         <f>IF(FALSE,1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1898,6 +1935,7 @@
       </c>
       <c r="C5" s="0">
         <f>IF(TRUE,,1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1908,106 +1946,127 @@
       </c>
       <c r="C6" s="0">
         <f>IF(A6,1,2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="0">
+      <c r="C7" s="0" t="b">
         <f>AND(A1&gt;5,A2&gt;5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="0">
+      <c r="C8" s="0" t="b">
         <f>AND(A1:A5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="0">
+      <c r="C9" s="0" t="b">
         <f>OR(A5,A3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="0">
+      <c r="C10" s="0" t="b">
         <f>OR(A5:A6,FALSE)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="0">
+      <c r="C11" s="0" t="b">
         <f>NOT(A5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="0">
+      <c r="C12" s="0" t="e">
         <f>AND(A3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="0">
+      <c r="C13" s="0" t="e">
         <f>AND(A6)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="0" cm="1">
+      <c r="C14" s="0" t="str" cm="1">
         <f t="array" ref="C14">_xlfn.IFS(A1&gt;15,"big",A1&gt;5,"mid",TRUE,"small")</f>
+        <v>mid</v>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="0" cm="1">
+      <c r="C15" s="0" t="e" cm="1">
         <f t="array" ref="C15">_xlfn.IFS(A1&gt;15,"big")</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="0" cm="1">
+      <c r="C16" s="0" t="str" cm="1">
         <f t="array" ref="C16">CHOOSE(2,"a","b","c")</f>
+        <v>b</v>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="0" cm="1">
+      <c r="C17" s="0" t="str" cm="1">
         <f t="array" ref="C17">CHOOSE(2.9,"a","b","c")</f>
+        <v>b</v>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="0" cm="1">
+      <c r="C18" s="0" t="e" cm="1">
         <f t="array" ref="C18">CHOOSE(0,"a")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="0">
+      <c r="C19" s="0" t="b">
         <f>ISNUMBER(A1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="0">
+      <c r="C20" s="0" t="b">
         <f>ISNUMBER(A3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="0">
+      <c r="C21" s="0" t="b">
         <f>ISNUMBER(1/0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="0">
+      <c r="C22" s="0" t="b">
         <f>ISBLANK(A9)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="0">
+      <c r="C23" s="0" t="b">
         <f>ISBLANK(A1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="0">
+      <c r="C24" s="0" t="b">
         <f>ISNUMBER(A6)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="0">
+      <c r="C25" s="0" t="e">
         <f>IF(1/0,1,2)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="0">
+      <c r="C26" s="0" t="e">
         <f>AND(TRUE,1/0)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="27">
@@ -2033,6 +2092,7 @@
       </c>
       <c r="C1" s="0">
         <f>SUM(A1:A6)</f>
+        <v>60</v>
       </c>
     </row>
     <row r="2">
@@ -2044,6 +2104,7 @@
       </c>
       <c r="C2" s="0">
         <f>SUM(A1,"5",TRUE)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2054,6 +2115,7 @@
       </c>
       <c r="C3" s="0">
         <f>SUM(A3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2063,196 +2125,235 @@
       <c r="B4" s="0">
         <v>4</v>
       </c>
-      <c r="C4" s="0">
+      <c r="C4" s="0" t="e">
         <f>SUM("x")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" s="0">
         <f>MIN(A1:A6)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0">
+      <c r="A6" s="0" t="b">
         <f>TRUE</f>
+        <v>1</v>
       </c>
       <c r="C6" s="0">
         <f>MAX(A1:A6)</f>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" s="0">
         <f>MIN(A3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" s="0">
         <f>AVERAGE(A1:A6)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="0">
+      <c r="C9" s="0" t="e">
         <f>AVERAGE(A3)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" s="0">
         <f>ABS(-3.5)</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="0">
         <f>INT(-1.5)</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" s="0">
         <f>INT(1.5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" s="0">
         <f>MOD(-7,3)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="0">
         <f>MOD(7,-3)</f>
+        <v>-2</v>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="0">
+      <c r="C15" s="0" t="e">
         <f>MOD(7,0)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="16">
       <c r="C16" s="0">
         <f>MOD(5.5,2)</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="0">
         <f>ROUND(2.675,2)</f>
+        <v>2.68</v>
       </c>
     </row>
     <row r="18">
       <c r="C18" s="0">
         <f>ROUND(-2.5,0)</f>
+        <v>-3</v>
       </c>
     </row>
     <row r="19">
       <c r="C19" s="0">
         <f>ROUND(1234.5678,-2)</f>
+        <v>1200</v>
       </c>
     </row>
     <row r="20">
       <c r="C20" s="0">
         <f>ROUND(1.234,1.9)</f>
+        <v>1.2</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" s="0">
         <f>ROUND(0.5,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="0">
         <f>ROUND(1.005,2)</f>
+        <v>1.01</v>
       </c>
     </row>
     <row r="23">
       <c r="C23" s="0">
         <f>ROW()</f>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="C24" s="0">
         <f>COLUMN()</f>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="C25" s="0">
         <f>ROW(A4)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="C26" s="0">
         <f>COLUMN(B1:C2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="0">
         <f>SIN(0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="C28" s="0">
         <f>SIN(1)</f>
+        <v>0.8414709848078965</v>
       </c>
     </row>
     <row r="29">
       <c r="C29" s="0">
         <f>SUMIF(A1:A6,"&gt;15")</f>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
       <c r="C30" s="0">
         <f>SUMIF(A1:A6,"&gt;15",B1:B6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="0">
         <f>COUNTIF(A1:A6,"&gt;15")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="C32" s="0">
         <f>COUNTIF(A1:A6,"x")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="C33" s="0">
         <f>COUNTIF(A1:A8,"")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="C34" s="0">
         <f>COUNTIF(A1:A6,"&lt;&gt;10")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="C35" s="0">
         <f>COUNTIF(A1:A6,"*")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="C36" s="0">
         <f>COUNTIF(A1:A6,10)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="C37" s="0">
         <f>COUNTIF(A1:A6,TRUE)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="C38" s="0">
         <f>SUMIF(A1:A6,"x",B1:B6)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="C39" s="0">
         <f>COUNTIF(B1:B4,"&lt;&gt;")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="C40" s="0">
         <f>SUM(Output!A1,logic!A1)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="C41" s="0">
         <f>SUM(Output:logic!A1)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -2273,6 +2374,7 @@
     <row r="45">
       <c r="C45" s="0">
         <f>SUM(C1:C3)</f>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/recalc/subset.xlsx
+++ b/scripts/recalc/subset.xlsx
@@ -11,7 +11,7 @@
     <sheet name="math" sheetId="4" r:id="rIdFrazaro4"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.8.1; sentences sha256:AC5301DBC1F55220FFDA023604667E1AB429335BDA03D9902519B1335DA93B37 over 4455 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.10.1; sentences sha256:AC5301DBC1F55220FFDA023604667E1AB429335BDA03D9902519B1335DA93B37 over 4455 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -2359,6 +2359,7 @@
     <row r="42">
       <c r="C42" s="0">
         <f>VLOOKUP(10,A1:B2,2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2369,6 +2370,7 @@
     <row r="44">
       <c r="C44" s="0">
         <f>C42+1</f>
+        <v>2</v>
       </c>
     </row>
     <row r="45">

--- a/scripts/recalc/subset.xlsx
+++ b/scripts/recalc/subset.xlsx
@@ -2070,8 +2070,9 @@
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="0">
+      <c r="C27" s="0" t="e">
         <f>IF(A1&gt;5,A1:A2,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/recalc/subset.xlsx
+++ b/scripts/recalc/subset.xlsx
@@ -2364,8 +2364,9 @@
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="0">
+      <c r="C43" s="0" t="str">
         <f>CONCATENATE("a","b")</f>
+        <v>ab</v>
       </c>
     </row>
     <row r="44">
